--- a/Models/КРС/Датасет по КРС wide.xlsx
+++ b/Models/КРС/Датасет по КРС wide.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U121"/>
+  <dimension ref="A1:U128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7877,6 +7877,475 @@
         <v>29353.24</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>3947.99</v>
+      </c>
+      <c r="C122" t="n">
+        <v>4466.24</v>
+      </c>
+      <c r="D122" t="n">
+        <v>2992.34</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1583.87</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1594.05</v>
+      </c>
+      <c r="G122" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H122" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I122" t="n">
+        <v>663.61</v>
+      </c>
+      <c r="J122" t="n">
+        <v>2386.42</v>
+      </c>
+      <c r="K122" t="n">
+        <v>2582.26</v>
+      </c>
+      <c r="L122" t="n">
+        <v>2251.02</v>
+      </c>
+      <c r="M122" t="n">
+        <v>2922.22</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1341.74</v>
+      </c>
+      <c r="O122" t="n">
+        <v>99.24000000000001</v>
+      </c>
+      <c r="P122" t="n">
+        <v>1999.86</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>2489.12</v>
+      </c>
+      <c r="R122" t="n">
+        <v>1319.15</v>
+      </c>
+      <c r="S122" t="n">
+        <v>2478.9</v>
+      </c>
+      <c r="T122" t="n">
+        <v>4007.77</v>
+      </c>
+      <c r="U122" t="n">
+        <v>8467.16</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>3588.93</v>
+      </c>
+      <c r="C123" t="n">
+        <v>4548.23</v>
+      </c>
+      <c r="D123" t="n">
+        <v>2824.69</v>
+      </c>
+      <c r="E123" t="n">
+        <v>2020.86</v>
+      </c>
+      <c r="F123" t="n">
+        <v>2704.93</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H123" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I123" t="n">
+        <v>623.5700000000001</v>
+      </c>
+      <c r="J123" t="n">
+        <v>3163.3</v>
+      </c>
+      <c r="K123" t="n">
+        <v>3443.42</v>
+      </c>
+      <c r="L123" t="n">
+        <v>1655.31</v>
+      </c>
+      <c r="M123" t="n">
+        <v>3988.12</v>
+      </c>
+      <c r="N123" t="n">
+        <v>1075.34</v>
+      </c>
+      <c r="O123" t="n">
+        <v>132.08</v>
+      </c>
+      <c r="P123" t="n">
+        <v>2813.21</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>1770.35</v>
+      </c>
+      <c r="R123" t="n">
+        <v>464.08</v>
+      </c>
+      <c r="S123" t="n">
+        <v>2439.47</v>
+      </c>
+      <c r="T123" t="n">
+        <v>2335.19</v>
+      </c>
+      <c r="U123" t="n">
+        <v>8032.34</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>4315.53</v>
+      </c>
+      <c r="C124" t="n">
+        <v>6574.41</v>
+      </c>
+      <c r="D124" t="n">
+        <v>8660.450000000001</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1740.22</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2809.92</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H124" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I124" t="n">
+        <v>400.39</v>
+      </c>
+      <c r="J124" t="n">
+        <v>2715</v>
+      </c>
+      <c r="K124" t="n">
+        <v>4863.53</v>
+      </c>
+      <c r="L124" t="n">
+        <v>2404.24</v>
+      </c>
+      <c r="M124" t="n">
+        <v>3137.83</v>
+      </c>
+      <c r="N124" t="n">
+        <v>1109.61</v>
+      </c>
+      <c r="O124" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="P124" t="n">
+        <v>3152.38</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>7699.85</v>
+      </c>
+      <c r="R124" t="n">
+        <v>401.05</v>
+      </c>
+      <c r="S124" t="n">
+        <v>2864.2</v>
+      </c>
+      <c r="T124" t="n">
+        <v>2064.27</v>
+      </c>
+      <c r="U124" t="n">
+        <v>8225.02</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>3934.11</v>
+      </c>
+      <c r="C125" t="n">
+        <v>5766.309999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>2975.6</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1429.08</v>
+      </c>
+      <c r="F125" t="n">
+        <v>2204.76</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>2</v>
+      </c>
+      <c r="I125" t="n">
+        <v>403.4</v>
+      </c>
+      <c r="J125" t="n">
+        <v>3245.04</v>
+      </c>
+      <c r="K125" t="n">
+        <v>3999.99</v>
+      </c>
+      <c r="L125" t="n">
+        <v>1792.75</v>
+      </c>
+      <c r="M125" t="n">
+        <v>3184.39</v>
+      </c>
+      <c r="N125" t="n">
+        <v>1429.88</v>
+      </c>
+      <c r="O125" t="n">
+        <v>279.48</v>
+      </c>
+      <c r="P125" t="n">
+        <v>2634.39</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>2296.43</v>
+      </c>
+      <c r="R125" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="S125" t="n">
+        <v>2872.67</v>
+      </c>
+      <c r="T125" t="n">
+        <v>1625.97</v>
+      </c>
+      <c r="U125" t="n">
+        <v>6628.299999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>3766.97</v>
+      </c>
+      <c r="C126" t="n">
+        <v>5446.24</v>
+      </c>
+      <c r="D126" t="n">
+        <v>4823.44</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1686.36</v>
+      </c>
+      <c r="F126" t="n">
+        <v>2856.12</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I126" t="n">
+        <v>435.75</v>
+      </c>
+      <c r="J126" t="n">
+        <v>3464.3</v>
+      </c>
+      <c r="K126" t="n">
+        <v>4231.860000000001</v>
+      </c>
+      <c r="L126" t="n">
+        <v>2202.71</v>
+      </c>
+      <c r="M126" t="n">
+        <v>4128.53</v>
+      </c>
+      <c r="N126" t="n">
+        <v>1463.98</v>
+      </c>
+      <c r="O126" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="P126" t="n">
+        <v>2757.33</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>2733.24</v>
+      </c>
+      <c r="R126" t="n">
+        <v>443.45</v>
+      </c>
+      <c r="S126" t="n">
+        <v>2706.78</v>
+      </c>
+      <c r="T126" t="n">
+        <v>1849.39</v>
+      </c>
+      <c r="U126" t="n">
+        <v>7697.58</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>4346.53</v>
+      </c>
+      <c r="C127" t="n">
+        <v>7109.86</v>
+      </c>
+      <c r="D127" t="n">
+        <v>14601.52</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1765.1</v>
+      </c>
+      <c r="F127" t="n">
+        <v>6147.46</v>
+      </c>
+      <c r="G127" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H127" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I127" t="n">
+        <v>517.7</v>
+      </c>
+      <c r="J127" t="n">
+        <v>6448.97</v>
+      </c>
+      <c r="K127" t="n">
+        <v>8235.66</v>
+      </c>
+      <c r="L127" t="n">
+        <v>6945.26</v>
+      </c>
+      <c r="M127" t="n">
+        <v>4248.12</v>
+      </c>
+      <c r="N127" t="n">
+        <v>1578.15</v>
+      </c>
+      <c r="O127" t="n">
+        <v>226</v>
+      </c>
+      <c r="P127" t="n">
+        <v>6965.91</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>9527.940000000001</v>
+      </c>
+      <c r="R127" t="n">
+        <v>854.7</v>
+      </c>
+      <c r="S127" t="n">
+        <v>4220.25</v>
+      </c>
+      <c r="T127" t="n">
+        <v>1416.17</v>
+      </c>
+      <c r="U127" t="n">
+        <v>9167.360000000001</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>2446.61</v>
+      </c>
+      <c r="C128" t="n">
+        <v>3555.44</v>
+      </c>
+      <c r="D128" t="n">
+        <v>2819.28</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1007.1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>3723.94</v>
+      </c>
+      <c r="G128" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I128" t="n">
+        <v>379.9</v>
+      </c>
+      <c r="J128" t="n">
+        <v>2419.61</v>
+      </c>
+      <c r="K128" t="n">
+        <v>3753.95</v>
+      </c>
+      <c r="L128" t="n">
+        <v>2125.57</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1555.87</v>
+      </c>
+      <c r="N128" t="n">
+        <v>1481.05</v>
+      </c>
+      <c r="O128" t="n">
+        <v>98.66</v>
+      </c>
+      <c r="P128" t="n">
+        <v>2293.91</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>1344.41</v>
+      </c>
+      <c r="R128" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="S128" t="n">
+        <v>4780.77</v>
+      </c>
+      <c r="T128" t="n">
+        <v>2324.16</v>
+      </c>
+      <c r="U128" t="n">
+        <v>8580.290000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
